--- a/archivos_vqd/Listado de VQDs Retencion.xlsx
+++ b/archivos_vqd/Listado de VQDs Retencion.xlsx
@@ -409,13 +409,13 @@
     <col min="4" max="4" style="5" width="42.29071428571429" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -423,7 +423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -431,7 +431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -439,7 +439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
